--- a/jewel pcb/BOM.xlsx
+++ b/jewel pcb/BOM.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="BOM_Board2_ROL_2025-11-15" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="BOM_Board2_ROL_2025-11-16" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -49,7 +49,7 @@
     <t>Test-Point</t>
   </si>
   <si>
-    <t>5V,CH1,GND</t>
+    <t>5V,5VB,CH7,CH7B,GND,GNDB</t>
   </si>
   <si>
     <t>Test-Point-0.5mm</t>
@@ -61,19 +61,19 @@
     <t>2</t>
   </si>
   <si>
-    <t>ZX-SH1.0-3PLT</t>
+    <t>HC-1.0-3PLT</t>
   </si>
   <si>
     <t>CH7</t>
   </si>
   <si>
-    <t>CONN-SMD_3P-P1.00_HDGC_HDGC1002WV-S-3P</t>
-  </si>
-  <si>
-    <t>Megastar(兆星)</t>
-  </si>
-  <si>
-    <t>C7430452</t>
+    <t>CONN-SMD_3P-P1.00_HC-1.0-3PLT</t>
+  </si>
+  <si>
+    <t>HCTL(华灿天禄)</t>
+  </si>
+  <si>
+    <t>C2845371</t>
   </si>
   <si>
     <t>LCSC</t>
@@ -514,7 +514,7 @@
         <v>10</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
         <v>11</v>
